--- a/raw/Timetable_2026Autumn_2025CS.xlsx
+++ b/raw/Timetable_2026Autumn_2025CS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{857AB067-8100-4599-A593-0642FA9648CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D9308CC-50C6-491A-8110-F2AD1E80206A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025CS1" sheetId="2" r:id="rId1"/>
@@ -217,7 +217,7 @@
     <t>16       Sep.</t>
   </si>
   <si>
-    <t>B207</t>
+    <t>B310</t>
   </si>
   <si>
     <t>17       Sep.</t>
@@ -592,7 +592,7 @@
     <t xml:space="preserve">Programming III (C++) </t>
   </si>
   <si>
-    <t>B209</t>
+    <t>B311</t>
   </si>
   <si>
     <t>WANG Chenguang</t>
@@ -12558,7 +12558,7 @@
         <v>43</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>42</v>
@@ -12567,7 +12567,7 @@
         <v>43</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>42</v>
@@ -12576,7 +12576,7 @@
         <v>43</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P22" s="2"/>
       <c r="Q22" s="4"/>
@@ -12630,7 +12630,7 @@
         <v>43</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J24" s="23" t="s">
         <v>42</v>
@@ -12639,7 +12639,7 @@
         <v>43</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>42</v>
@@ -12648,7 +12648,7 @@
         <v>43</v>
       </c>
       <c r="O24" s="25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P24" s="21"/>
       <c r="Q24" s="21"/>
@@ -13273,7 +13273,7 @@
         <v>43</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>42</v>
@@ -13282,7 +13282,7 @@
         <v>43</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M43" s="11" t="s">
         <v>42</v>
@@ -13291,7 +13291,7 @@
         <v>43</v>
       </c>
       <c r="O43" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="13"/>
@@ -13582,7 +13582,7 @@
         <v>43</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>42</v>
@@ -13591,7 +13591,7 @@
         <v>43</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>42</v>
@@ -13600,7 +13600,7 @@
         <v>43</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P50" s="2"/>
       <c r="Q50" s="4"/>
@@ -13849,7 +13849,7 @@
         <v>43</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>42</v>
@@ -13858,7 +13858,7 @@
         <v>43</v>
       </c>
       <c r="L57" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M57" s="11" t="s">
         <v>42</v>
@@ -13867,7 +13867,7 @@
         <v>43</v>
       </c>
       <c r="O57" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P57" s="11"/>
       <c r="Q57" s="13"/>
@@ -14134,7 +14134,7 @@
         <v>43</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>42</v>
@@ -14143,7 +14143,7 @@
         <v>43</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>42</v>
@@ -14152,7 +14152,7 @@
         <v>43</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P64" s="2"/>
       <c r="Q64" s="4"/>
@@ -14437,7 +14437,7 @@
         <v>43</v>
       </c>
       <c r="I71" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>42</v>
@@ -14446,7 +14446,7 @@
         <v>43</v>
       </c>
       <c r="L71" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M71" s="11" t="s">
         <v>42</v>
@@ -14455,7 +14455,7 @@
         <v>43</v>
       </c>
       <c r="O71" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P71" s="11"/>
       <c r="Q71" s="13"/>
@@ -14728,7 +14728,7 @@
         <v>43</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>45</v>
@@ -14737,7 +14737,7 @@
         <v>43</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>45</v>
@@ -14746,7 +14746,7 @@
         <v>43</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P78" s="60"/>
       <c r="Q78" s="61"/>
